--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/BonusCalist001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/BonusCalist001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,9 +24,6 @@
     <t>数据状态</t>
   </si>
   <si>
-    <t>产品子代码</t>
-  </si>
-  <si>
     <t>产品名称</t>
   </si>
   <si>
@@ -97,6 +94,10 @@
   </si>
   <si>
     <t>错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子产品代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -104,7 +105,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +116,15 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -141,11 +151,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,65 +459,65 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
